--- a/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
+++ b/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
@@ -13,12 +13,13 @@
     <sheet name="Minute-by-minute" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Meal plan" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Places &amp; maps" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Pros &amp; cons" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Challenges" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Do's &amp; don'ts" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Visa documents" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Inclusions" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Practical info" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Entry tickets" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Pros &amp; cons" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Challenges" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Do's &amp; don'ts" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Visa documents" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Inclusions" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Practical info" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Minute-by-minute'!$A$2:$P$224</definedName>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="790">
   <si>
     <t xml:space="preserve">London Europe Yatra – Minute-by-minute itinerary (DRAFT for fine-tuning)</t>
   </si>
@@ -1691,6 +1692,258 @@
     <t xml:space="preserve">Rome Fiumicino Airport</t>
   </si>
   <si>
+    <t xml:space="preserve">Entry tickets – adult price per person (official 2026 rates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked 2026-10-22. Edit a price or an exchange rate and the INR columns and totals update.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR per 1 GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR per 1 EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INR per 1 CHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In plan?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price (local)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price (INR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lion King, Lyceum (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group 20+ Stalls/Royal Circle; group shows Tue–Fri only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christ Church, Oxford (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekday; 65+ £20.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodleian Library 60-min tour (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourton Model Village (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over 60 £4.50; card only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group 10+; £29 online standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thames boat London Eye → Tower (Uber Boat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online single; 10% off groups 10+; seniors 50% off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower of London (Crown Jewels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT VERIFIED – official site blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online from-price; walk-up £39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seine cruise – Bateaux Parisiens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online; €20 on the day (partly verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel Tower – lift to 2nd floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youth 12–24 €11.80; child €6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disneyland Paris 1 day (Option B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€56–110 by date; NOT VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louvre (non-EU rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group €28 + €90 fee per 7–20 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atomium inside (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group 20+; standard €17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amsterdam canal cruise 75 min (Blue Boat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus passenger tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Kat windmill, Zaanse Schans (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cologne Cathedral inside (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New charge since 1 Jul 2026; free during services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Titisee boat (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 25 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhine Falls – Schloss Laufen platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child CHF 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhine Falls boat to the rock (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not for seniors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Titlis return (group rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% off CHF 102 for groups 10+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titlis Ice Flyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Lucerne 1-hour cruise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBC – no 2026 fare published; groups@lakelucerne.ch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luzern–Interlaken Express 2nd class (group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHF 23.80 + CHF 16 reservation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Como boat Como ↔ Cernobbio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return; groups/seniors €4.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan Duomo cathedral + museum (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraces lift €18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice vaporetto 1-day pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single €9.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice gondola 30 min (per person, 5/boat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~€90 per gondola; NOT VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doge's Palace (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online 30 days ahead; €35 otherwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaning Tower of Pisa climb (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes Cathedral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florence Duomo Brunelleschi Pass (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cathedral itself free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vatican Museums &amp; Sistine Chapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€20 + €5 booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colosseum + Forum + Palatine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under 18 free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevi Fountain basin access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since Feb 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantheon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total – tickets in the plan (per adult)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total – optional extras if all taken (per adult)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group costs (not per person): Zaanse Schans coach parking €35–55/day; Volendam coach parking €15–25; Louvre group fee €90 per 7–20; Dover–Calais ferry by quote; Venice access fee – overnight guests in Mestre exempt but must register.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pros</t>
   </si>
   <si>
@@ -2100,9 +2353,6 @@
   </si>
   <si>
     <t xml:space="preserve">London 14–23 °C, showers possible; Paris/Brussels/Amsterdam 15–25 °C; Black Forest/Zurich 14–25 °C; Titlis summit 0–5 °C; Milan/Venice/Florence/Rome 22–35 °C. Sunset ~21:15 (London) to ~20:40 (Rome).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency</t>
   </si>
   <si>
     <t xml:space="preserve">UK: GBP (£). France, Belgium, Netherlands, Germany, Italy, Vatican: EUR (€). Switzerland: CHF (EUR widely accepted at a poor rate). A multi-currency forex card plus a little cash in each.</t>
@@ -2160,14 +2410,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="[h]:mm"/>
     <numFmt numFmtId="168" formatCode="hh:mm"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2244,6 +2495,20 @@
       <u val="single"/>
       <sz val="9"/>
       <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2330,7 +2595,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2444,6 +2709,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2889,68 +3162,119 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>674</v>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>677</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>678</v>
+      <c r="A3" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>679</v>
+        <v>737</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>738</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>739</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B7" s="6"/>
+        <v>741</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>683</v>
-      </c>
-      <c r="B8" s="6"/>
+        <v>743</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>684</v>
-      </c>
-      <c r="B9" s="6"/>
+        <v>745</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="C14" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2968,6 +3292,85 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B9" s="6"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2977,42 +3380,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>685</v>
+        <v>769</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>686</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>687</v>
+        <v>771</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>688</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>689</v>
+        <v>558</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>690</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>691</v>
+        <v>774</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>692</v>
+        <v>775</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>693</v>
+        <v>776</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>694</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3020,31 +3423,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>695</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>696</v>
+        <v>779</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>697</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>698</v>
+        <v>781</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>699</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>700</v>
+        <v>783</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>701</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3052,23 +3455,23 @@
         <v>169</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>702</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>703</v>
+        <v>786</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>704</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>706</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -16955,201 +17358,1062 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>126.78</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>106.13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>114.66</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>567</v>
+      <c r="G8" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>569</v>
+        <v>562</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <f aca="false">IF(E10="","",E10*$B$4)</f>
+        <v>5705.1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>571</v>
+        <v>562</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <f aca="false">IF(E11="","",E11*$B$4)</f>
+        <v>2909.601</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>573</v>
+        <v>562</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <f aca="false">IF(E12="","",E12*$B$4)</f>
+        <v>2218.65</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>575</v>
+        <v>562</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <f aca="false">IF(E13="","",E13*$B$4)</f>
+        <v>627.561</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>576</v>
+        <v>150</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>577</v>
+        <v>572</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <f aca="false">IF(E14="","",E14*$B$4)</f>
+        <v>3296.28</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>579</v>
+        <v>572</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <f aca="false">IF(E15="","",E15*$B$4)</f>
+        <v>1483.326</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>581</v>
+        <v>572</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <f aca="false">IF(E16="","",E16*$B$4)</f>
+        <v>4690.86</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>582</v>
+        <v>163</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>583</v>
+        <v>572</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>27</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <f aca="false">IF(E17="","",E17*$B$4)</f>
+        <v>3423.06</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <f aca="false">IF(E18="","",E18*$B$5)</f>
+        <v>1910.34</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <f aca="false">IF(E19="","",E19*$B$5)</f>
+        <v>2494.055</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>56</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <f aca="false">IF(E20="","",E20*$B$5)</f>
+        <v>5943.28</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>32</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <f aca="false">IF(E21="","",E21*$B$5)</f>
+        <v>3396.16</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <f aca="false">IF(E22="","",E22*$B$5)</f>
+        <v>1591.95</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <f aca="false">IF(E23="","",E23*$B$5)</f>
+        <v>2759.38</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <f aca="false">IF(E24="","",E24*$B$5)</f>
+        <v>795.975</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <f aca="false">IF(E25="","",E25*$B$5)</f>
+        <v>1273.56</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <f aca="false">IF(E26="","",E26*$B$5)</f>
+        <v>795.975</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <f aca="false">IF(E27="","",E27*$B$6)</f>
+        <v>573.3</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <f aca="false">IF(E28="","",E28*$B$6)</f>
+        <v>2579.85</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>81.6</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <f aca="false">IF(E29="","",E29*$B$6)</f>
+        <v>9356.256</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <f aca="false">IF(E30="","",E30*$B$6)</f>
+        <v>1375.92</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E31" s="30"/>
+      <c r="F31" s="8" t="str">
+        <f aca="false">IF(E31="","",E31*$B$6)</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <f aca="false">IF(E32="","",E32*$B$6)</f>
+        <v>4563.468</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <f aca="false">IF(E33="","",E33*$B$5)</f>
+        <v>636.78</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <f aca="false">IF(E34="","",E34*$B$5)</f>
+        <v>1061.3</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <f aca="false">IF(E35="","",E35*$B$5)</f>
+        <v>2653.25</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <f aca="false">IF(E36="","",E36*$B$5)</f>
+        <v>1910.34</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <f aca="false">IF(E37="","",E37*$B$5)</f>
+        <v>3183.9</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <f aca="false">IF(E38="","",E38*$B$5)</f>
+        <v>2122.6</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <f aca="false">IF(E39="","",E39*$B$5)</f>
+        <v>3183.9</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>585</v>
+      <c r="B40" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <f aca="false">IF(E40="","",E40*$B$5)</f>
+        <v>2653.25</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <f aca="false">IF(E41="","",E41*$B$5)</f>
+        <v>1910.34</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <f aca="false">IF(E42="","",E42*$B$5)</f>
+        <v>212.26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <f aca="false">IF(E43="","",E43*$B$5)</f>
+        <v>742.91</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6"/>
+      <c r="B44" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="12" t="n">
+        <f aca="false">SUMIFS(F10:F43,C10:C43,"Yes")</f>
+        <v>50041.535</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6"/>
+      <c r="B45" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="12" t="n">
+        <f aca="false">SUMIFS(F10:F43,C10:C43,"Optional")</f>
+        <v>33993.202</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="14" t="s">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H10" r:id="rId1" display="Open"/>
+    <hyperlink ref="H11" r:id="rId2" display="Open"/>
+    <hyperlink ref="H12" r:id="rId3" display="Open"/>
+    <hyperlink ref="H13" r:id="rId4" display="Open"/>
+    <hyperlink ref="H14" r:id="rId5" display="Open"/>
+    <hyperlink ref="H15" r:id="rId6" display="Open"/>
+    <hyperlink ref="H16" r:id="rId7" display="Open"/>
+    <hyperlink ref="H17" r:id="rId8" display="Open"/>
+    <hyperlink ref="H18" r:id="rId9" display="Open"/>
+    <hyperlink ref="H19" r:id="rId10" display="Open"/>
+    <hyperlink ref="H20" r:id="rId11" display="Open"/>
+    <hyperlink ref="H21" r:id="rId12" display="Open"/>
+    <hyperlink ref="H22" r:id="rId13" display="Open"/>
+    <hyperlink ref="H23" r:id="rId14" display="Open"/>
+    <hyperlink ref="H24" r:id="rId15" display="Open"/>
+    <hyperlink ref="H25" r:id="rId16" display="Open"/>
+    <hyperlink ref="H26" r:id="rId17" display="Open"/>
+    <hyperlink ref="H27" r:id="rId18" display="Open"/>
+    <hyperlink ref="H28" r:id="rId19" display="Open"/>
+    <hyperlink ref="H29" r:id="rId20" display="Open"/>
+    <hyperlink ref="H30" r:id="rId21" display="Open"/>
+    <hyperlink ref="H31" r:id="rId22" display="Open"/>
+    <hyperlink ref="H32" r:id="rId23" display="Open"/>
+    <hyperlink ref="H33" r:id="rId24" display="Open"/>
+    <hyperlink ref="H34" r:id="rId25" display="Open"/>
+    <hyperlink ref="H35" r:id="rId26" display="Open"/>
+    <hyperlink ref="H37" r:id="rId27" display="Open"/>
+    <hyperlink ref="H38" r:id="rId28" display="Open"/>
+    <hyperlink ref="H39" r:id="rId29" display="Open"/>
+    <hyperlink ref="H40" r:id="rId30" display="Open"/>
+    <hyperlink ref="H41" r:id="rId31" display="Open"/>
+    <hyperlink ref="H42" r:id="rId32" display="Open"/>
+    <hyperlink ref="H43" r:id="rId33" display="Open"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -17165,155 +18429,198 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>586</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>587</v>
+        <v>636</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>589</v>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>590</v>
+        <v>638</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>592</v>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>595</v>
+        <v>641</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>598</v>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>599</v>
+        <v>644</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>601</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>604</v>
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>607</v>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>608</v>
+        <v>650</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>610</v>
+        <v>651</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>611</v>
+        <v>652</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>613</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>614</v>
+        <v>654</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>616</v>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>619</v>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>622</v>
+        <v>659</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>624</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -17332,111 +18639,156 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>625</v>
+        <v>670</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>671</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>674</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>629</v>
+        <v>676</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>677</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>631</v>
+        <v>679</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>632</v>
+        <v>680</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>633</v>
+        <v>682</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>634</v>
+        <v>683</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>635</v>
+        <v>685</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>686</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>637</v>
+        <v>688</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>689</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>639</v>
+        <v>691</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>640</v>
+        <v>692</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>641</v>
+        <v>694</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>642</v>
+        <v>695</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>643</v>
+        <v>697</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>701</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>703</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B14" s="6"/>
+        <v>706</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -17454,119 +18806,111 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>649</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>653</v>
+        <v>715</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="C5" s="6"/>
+        <v>716</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>655</v>
+        <v>717</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>657</v>
+        <v>719</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="C7" s="6"/>
+        <v>720</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>659</v>
+        <v>721</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="C8" s="6"/>
+        <v>722</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>661</v>
+        <v>723</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>662</v>
-      </c>
-      <c r="C9" s="6"/>
+        <v>724</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>663</v>
+        <v>725</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>665</v>
+        <v>727</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="C11" s="6"/>
+        <v>728</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>667</v>
+        <v>729</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>669</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>731</v>
+      </c>
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>671</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>732</v>
+      </c>
+      <c r="B14" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
+++ b/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
@@ -1249,19 +1249,19 @@
     <t xml:space="preserve">Titlis Xpress gondola + Rotair (revolving cable car) to 3,020 m: Glacier Cave, Cliff Walk (optional), snow play, group photo at the summit. Ice Flyer chairlift only if it is running in spring.</t>
   </si>
   <si>
-    <t xml:space="preserve">Altitude and cold: seniors go slowly and stay hydrated. Check the webcam and lift status the evening before.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indian restaurant at Titlis summit station (verify it is open)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indian restaurant at Titlis summit station (pre-book; verify it is open) – backup: Engelberg Indian restaurant</t>
+    <t xml:space="preserve">Summit station under construction until 2029 (limited wheelchair access). Ask sales@titlis.ch for 2027 maintenance dates. Check webcam and lift status the evening before.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Group Restaurant, Trübsee mid-station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Group Restaurant at Trübsee mid-station (moved down from the summit during construction; pre-book)</t>
   </si>
   <si>
     <t xml:space="preserve">Descent</t>
   </si>
   <si>
-    <t xml:space="preserve">Rotair and gondola back down to Engelberg.</t>
+    <t xml:space="preserve">Gondola from Trübsee back down to Engelberg.</t>
   </si>
   <si>
     <t xml:space="preserve">Lion Monument (Löwendenkmal), Lucerne</t>
@@ -1978,7 +1978,7 @@
     <t xml:space="preserve">Titlis Talstation, Engelberg</t>
   </si>
   <si>
-    <t xml:space="preserve">Titlis Bergstation Restaurant</t>
+    <t xml:space="preserve">Trübsee Titlis Engelberg</t>
   </si>
   <si>
     <t xml:space="preserve">Lucerne</t>
@@ -2731,10 +2731,10 @@
     <t xml:space="preserve">Details</t>
   </si>
   <si>
-    <t xml:space="preserve">Weather in late July</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London 14–23 °C, showers possible; Paris/Brussels/Amsterdam 15–25 °C; Black Forest/Zurich 14–25 °C; Titlis summit 0–5 °C; Milan/Venice/Florence/Rome 22–35 °C. Sunset ~21:15 (London) to ~20:40 (Rome).</t>
+    <t xml:space="preserve">Weather in late April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15–21 °C by day, 6–11 °C at night, rain on 3–5 days in 11. Titisee mornings near freezing. Titlis summit −2 to −7 °C with snow. Sunset 20:00–21:00.</t>
   </si>
   <si>
     <t xml:space="preserve">UK: GBP (£). France, Belgium, Netherlands, Germany, Italy, Vatican: EUR (€). Switzerland: CHF (EUR widely accepted at a poor rate). A multi-currency forex card plus a little cash in each.</t>
@@ -2752,7 +2752,7 @@
     <t xml:space="preserve">An international roaming pack or a Europe + UK eSIM. Switzerland is often excluded from EU packs, so check. Make WhatsApp the group channel.</t>
   </si>
   <si>
-    <t xml:space="preserve">UK = IST − 4 h 30 m (BST). France to Italy = IST − 3 h 30 m (CEST).</t>
+    <t xml:space="preserve">UK = IST − 4 h 30 m (BST). France to Italy = IST − 3 h 30 m (CEST). Abu Dhabi = IST − 1 h 30 m.</t>
   </si>
   <si>
     <t xml:space="preserve">Tipping</t>
@@ -2773,7 +2773,7 @@
     <t xml:space="preserve">Seats near the front, wheelchair booking at the Louvre, Vatican and airports, extra rest stops, a medicine pouch with prescriptions, an attendant ratio of 1:10, lifts used wherever available.</t>
   </si>
   <si>
-    <t xml:space="preserve">4 sets of comfortable clothes + 1 dhoti/saree set for temples, a light jacket + a warm fleece (Titlis), raincoat or umbrella, cap, sunglasses, walking shoes + slippers, tulasi beads, japa bag, small Gita, medicines for 20 days, ORS, sunscreen, an empty bottle, a small towel, a lock for suitcases, a laundry bag.</t>
+    <t xml:space="preserve">Warm jacket + fleece + thermal layer, gloves, woollen cap (Titlis), Ekadasi snacks for 17 Apr and 2 May, 4–5 sets of clothes + 1 dhoti/saree set for temples, raincoat or umbrella, cap, sunglasses, walking shoes + slippers, tulasi beads, japa bag, small Gita, medicines for 20 days, ORS, sunscreen, an empty bottle, a small towel, a lock for suitcases, a laundry bag.</t>
   </si>
   <si>
     <t xml:space="preserve">Water &amp; toilets</t>
@@ -2785,7 +2785,7 @@
     <t xml:space="preserve">Shopping &amp; VAT refund</t>
   </si>
   <si>
-    <t xml:space="preserve">Paris: perfumes and fashion; Switzerland: chocolates, watches, cuckoo clocks (Titisee); Italy: leather (Florence), Murano glass (Venice). Ask for a tax-free form and get it stamped at Rome airport before check-in.</t>
+    <t xml:space="preserve">Paris: perfumes and fashion; Switzerland: chocolates, watches, cuckoo clocks (Titisee); Italy: leather (Florence), Murano glass (Venice). Ask for a tax-free form and get it stamped at Malpensa customs before check-in.</t>
   </si>
 </sst>
 </file>
@@ -3967,7 +3967,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>898</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
         <v>258</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="11" t="n">
         <v>11</v>
       </c>

--- a/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
+++ b/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
@@ -649,7 +649,7 @@
     <t xml:space="preserve">Briefing</t>
   </si>
   <si>
-    <t xml:space="preserve">Joint welcome kirtan and briefing. Tomorrow: break fast (Dvadasi parana) 05:59–10:40 at breakfast (07:00–09:00); coach 09:00. Sunset tonight about 20:05; jet lag: sleep by 22:30.</t>
+    <t xml:space="preserve">Joint welcome kirtan and briefing. Tomorrow: break fast (Dvadasi parana) 05:59–10:40 at breakfast (08:00–09:00); coach 09:00. Sunset tonight about 20:05; jet lag: sleep by 22:30.</t>
   </si>
   <si>
     <t xml:space="preserve">DAY 2 · Sun</t>
@@ -667,7 +667,7 @@
     <t xml:space="preserve">Break the Ekadasi fast with grains at breakfast.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel – complimentary buffet (07:00–09:00) – Dvadasi break fast between 05:59 and 10:40 (London)</t>
+    <t xml:space="preserve">Hotel – complimentary buffet (08:00–09:00) – Dvadasi break fast between 05:59 and 10:40 (London)</t>
   </si>
   <si>
     <t xml:space="preserve">Bhaktivedanta Manor, ISKCON (Watford)</t>
@@ -733,7 +733,7 @@
     <t xml:space="preserve">DAY 3 · Mon</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel – complimentary buffet (07:00–09:00)</t>
+    <t xml:space="preserve">Hotel – complimentary buffet (08:00–09:00)</t>
   </si>
   <si>
     <t xml:space="preserve">Westminster – Big Ben &amp; Houses of Parliament</t>
@@ -1420,7 +1420,7 @@
     <t xml:space="preserve">Overnight: Florence</t>
   </si>
   <si>
-    <t xml:space="preserve">EXCEPTION to the 07:00–09:00 breakfast / 09:00 start: the only Vatican day needs the 06:30 train. With a 09:00 start the group reaches Rome at ~13:15 and loses the Colosseum interior.</t>
+    <t xml:space="preserve">EXCEPTION to the 08:00–09:00 breakfast / 09:00 start: the only Vatican day needs the 06:30 train. With a 09:00 start the group reaches Rome at ~13:15 and loses the Colosseum interior.</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel – breakfast boxes (ordered the evening before)</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H4" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A4)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I4" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A4)</f>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="H5" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A5)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I5" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A5)</f>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H6" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A6)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I6" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A6)</f>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="H7" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A7)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I7" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A7)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="H8" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A8)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I8" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A8)</f>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H9" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A9)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I9" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A9)</f>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="H10" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A10)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I10" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A10)</f>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="H11" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A11)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I11" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A11)</f>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H12" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A12)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I12" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A12)</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A13)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I13" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A13)</f>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H14" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A14)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I14" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A14)</f>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="H15" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A15)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I15" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A15)</f>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H17" s="23" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-minute'!$D$3:$D$234,'Minute-by-minute'!$A$3:$A$234,A17)</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="I17" s="23" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-minute'!$E$3:$E$234,'Minute-by-minute'!$A$3:$A$234,A17)</f>
@@ -6674,14 +6674,14 @@
         <v>166</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">ROUND(MOD(E18-D18,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>206</v>
@@ -6717,14 +6717,14 @@
         <v>166</v>
       </c>
       <c r="D19" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E19" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F19" s="35" t="n">
         <f aca="false">ROUND(MOD(E19-D19,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>208</v>
@@ -7244,14 +7244,14 @@
         <v>166</v>
       </c>
       <c r="D31" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E31" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">ROUND(MOD(E31-D31,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>206</v>
@@ -7287,14 +7287,14 @@
         <v>166</v>
       </c>
       <c r="D32" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E32" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F32" s="35" t="n">
         <f aca="false">ROUND(MOD(E32-D32,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G32" s="35" t="s">
         <v>208</v>
@@ -7947,14 +7947,14 @@
         <v>166</v>
       </c>
       <c r="D47" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E47" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F47" s="11" t="n">
         <f aca="false">ROUND(MOD(E47-D47,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G47" s="11" t="s">
         <v>206</v>
@@ -7990,14 +7990,14 @@
         <v>166</v>
       </c>
       <c r="D48" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E48" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F48" s="35" t="n">
         <f aca="false">ROUND(MOD(E48-D48,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>208</v>
@@ -8424,14 +8424,14 @@
         <v>277</v>
       </c>
       <c r="D58" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E58" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F58" s="11" t="n">
         <f aca="false">ROUND(MOD(E58-D58,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G58" s="11" t="s">
         <v>206</v>
@@ -8467,14 +8467,14 @@
         <v>277</v>
       </c>
       <c r="D59" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E59" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F59" s="35" t="n">
         <f aca="false">ROUND(MOD(E59-D59,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G59" s="35" t="s">
         <v>208</v>
@@ -9223,14 +9223,14 @@
         <v>277</v>
       </c>
       <c r="D76" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E76" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F76" s="11" t="n">
         <f aca="false">ROUND(MOD(E76-D76,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>206</v>
@@ -9266,14 +9266,14 @@
         <v>277</v>
       </c>
       <c r="D77" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E77" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F77" s="35" t="n">
         <f aca="false">ROUND(MOD(E77-D77,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G77" s="35" t="s">
         <v>208</v>
@@ -9879,14 +9879,14 @@
         <v>277</v>
       </c>
       <c r="D91" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E91" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F91" s="11" t="n">
         <f aca="false">ROUND(MOD(E91-D91,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G91" s="11" t="s">
         <v>206</v>
@@ -9922,14 +9922,14 @@
         <v>277</v>
       </c>
       <c r="D92" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E92" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F92" s="35" t="n">
         <f aca="false">ROUND(MOD(E92-D92,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>208</v>
@@ -10484,14 +10484,14 @@
         <v>277</v>
       </c>
       <c r="D105" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E105" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F105" s="11" t="n">
         <f aca="false">ROUND(MOD(E105-D105,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>206</v>
@@ -10527,14 +10527,14 @@
         <v>277</v>
       </c>
       <c r="D106" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E106" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F106" s="35" t="n">
         <f aca="false">ROUND(MOD(E106-D106,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G106" s="35" t="s">
         <v>208</v>
@@ -11046,14 +11046,14 @@
         <v>277</v>
       </c>
       <c r="D118" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E118" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F118" s="11" t="n">
         <f aca="false">ROUND(MOD(E118-D118,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G118" s="11" t="s">
         <v>206</v>
@@ -11089,14 +11089,14 @@
         <v>277</v>
       </c>
       <c r="D119" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E119" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F119" s="35" t="n">
         <f aca="false">ROUND(MOD(E119-D119,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>208</v>
@@ -11661,14 +11661,14 @@
         <v>277</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F132" s="11" t="n">
         <f aca="false">ROUND(MOD(E132-D132,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>206</v>
@@ -11704,14 +11704,14 @@
         <v>277</v>
       </c>
       <c r="D133" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E133" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F133" s="35" t="n">
         <f aca="false">ROUND(MOD(E133-D133,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G133" s="35" t="s">
         <v>208</v>
@@ -12309,14 +12309,14 @@
         <v>277</v>
       </c>
       <c r="D147" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E147" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F147" s="11" t="n">
         <f aca="false">ROUND(MOD(E147-D147,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G147" s="11" t="s">
         <v>206</v>
@@ -12352,14 +12352,14 @@
         <v>277</v>
       </c>
       <c r="D148" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E148" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F148" s="35" t="n">
         <f aca="false">ROUND(MOD(E148-D148,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G148" s="35" t="s">
         <v>208</v>
@@ -13006,14 +13006,14 @@
         <v>277</v>
       </c>
       <c r="D163" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E163" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F163" s="11" t="n">
         <f aca="false">ROUND(MOD(E163-D163,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G163" s="11" t="s">
         <v>206</v>
@@ -13049,14 +13049,14 @@
         <v>277</v>
       </c>
       <c r="D164" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E164" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F164" s="35" t="n">
         <f aca="false">ROUND(MOD(E164-D164,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G164" s="35" t="s">
         <v>208</v>
@@ -13566,14 +13566,14 @@
         <v>277</v>
       </c>
       <c r="D176" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E176" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F176" s="11" t="n">
         <f aca="false">ROUND(MOD(E176-D176,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G176" s="11" t="s">
         <v>206</v>
@@ -13609,14 +13609,14 @@
         <v>277</v>
       </c>
       <c r="D177" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E177" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F177" s="35" t="n">
         <f aca="false">ROUND(MOD(E177-D177,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G177" s="35" t="s">
         <v>208</v>
@@ -15115,14 +15115,14 @@
         <v>277</v>
       </c>
       <c r="D211" s="23" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="E211" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F211" s="11" t="n">
         <f aca="false">ROUND(MOD(E211-D211,1)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G211" s="11" t="s">
         <v>206</v>
@@ -15158,14 +15158,14 @@
         <v>277</v>
       </c>
       <c r="D212" s="37" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E212" s="37" t="n">
         <v>0.375</v>
       </c>
       <c r="F212" s="35" t="n">
         <f aca="false">ROUND(MOD(E212-D212,1)*1440,0)</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G212" s="35" t="s">
         <v>208</v>
@@ -16530,7 +16530,7 @@
         <v>208</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>0.375</v>
@@ -16624,7 +16624,7 @@
         <v>208</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>0.375</v>
@@ -16716,7 +16716,7 @@
         <v>208</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E11" s="23" t="n">
         <v>0.375</v>
@@ -16808,7 +16808,7 @@
         <v>208</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0.375</v>
@@ -16900,7 +16900,7 @@
         <v>208</v>
       </c>
       <c r="D17" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E17" s="23" t="n">
         <v>0.375</v>
@@ -16992,7 +16992,7 @@
         <v>208</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>0.375</v>
@@ -17082,7 +17082,7 @@
         <v>208</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E23" s="23" t="n">
         <v>0.375</v>
@@ -17172,7 +17172,7 @@
         <v>208</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E26" s="23" t="n">
         <v>0.375</v>
@@ -17264,7 +17264,7 @@
         <v>208</v>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E29" s="23" t="n">
         <v>0.375</v>
@@ -17354,7 +17354,7 @@
         <v>208</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E32" s="23" t="n">
         <v>0.375</v>
@@ -17446,7 +17446,7 @@
         <v>208</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E35" s="23" t="n">
         <v>0.375</v>
@@ -17536,7 +17536,7 @@
         <v>208</v>
       </c>
       <c r="D38" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>0.375</v>
@@ -17722,7 +17722,7 @@
         <v>208</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>0.291666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E44" s="23" t="n">
         <v>0.375</v>

--- a/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
+++ b/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
@@ -15,12 +15,13 @@
     <sheet name="Meal plan" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Places &amp; maps" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Entry tickets" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Pros &amp; cons" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Challenges" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Do's &amp; don'ts" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Visa documents" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Inclusions" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Practical info" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Booking guide" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pros &amp; cons" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Challenges" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Do's &amp; don'ts" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Visa documents" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Inclusions" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Practical info" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Minute-by-minute'!$A$2:$P$247</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3126" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="1080">
   <si>
     <t xml:space="preserve">London Europe Yatra – Minute-by-minute itinerary (DRAFT for fine-tuning)</t>
   </si>
@@ -2317,7 +2318,7 @@
     <t xml:space="preserve">Keukenhof (group rate, 20+)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT VERIFIED on keukenhof.nl; ~€21.50 online single; coach parking free</t>
+    <t xml:space="preserve">Group rate 20+ (online shop); €26.50 at the gate</t>
   </si>
   <si>
     <t xml:space="preserve">Cologne Cathedral inside (optional)</t>
@@ -2335,7 +2336,7 @@
     <t xml:space="preserve">Rhine Falls – Schloss Laufen platforms</t>
   </si>
   <si>
-    <t xml:space="preserve">Child CHF 3</t>
+    <t xml:space="preserve">Group 30+ CHF 2 (15–29: CHF 3); adult CHF 5; buy at the visitor centre</t>
   </si>
   <si>
     <t xml:space="preserve">Rhine Falls boat to the rock (optional)</t>
@@ -2347,7 +2348,7 @@
     <t xml:space="preserve">Mount Titlis return (group rate)</t>
   </si>
   <si>
-    <t xml:space="preserve">20% off CHF 102 for groups 10+</t>
+    <t xml:space="preserve">Titlis site: 10% group discount (10+) on CHF 102 – an older Engelberg page said 20%; confirm with reservation@titlis.ch</t>
   </si>
   <si>
     <t xml:space="preserve">Titlis Ice Flyer (optional, if running in spring)</t>
@@ -2359,7 +2360,7 @@
     <t xml:space="preserve">Lake Lucerne 1-hour cruise</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC – no 2026 fare published; groups@lakelucerne.ch</t>
+    <t xml:space="preserve">No 2026 fare published; groups of 10+ get 30% off; groups@lakelucerne.ch</t>
   </si>
   <si>
     <t xml:space="preserve">Luzern–Interlaken Express 2nd class (group)</t>
@@ -2443,6 +2444,363 @@
     <t xml:space="preserve">Group costs (not per person): Zaanse Schans coach parking €35–55/day; Volendam coach parking €15–25; Louvre group fee €90 per 7–20; Dover–Calais ferry by quote; Venice access fee – overnight guests in Mestre exempt but must register.</t>
   </si>
   <si>
+    <t xml:space="preserve">Where to book every ticket – official sites and group desks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official booking link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When to book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://akshayapatra.org.uk/contact/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free; visits by appointment only (tel. 020 800 48743).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write now; confirm 2 weeks before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.krishnatemple.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free; tell the Manor the numbers and arrival time (tel. 01923 851000); prasadam by donation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 month before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.madametussauds.com/london/tickets/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group rate; ask for a combined London Eye + Madame Tussauds group price; timed entry 15:00.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60–90 days before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changing of the Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.householddivision.org.uk/changing-the-guard-calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free, no booking. Mon/Wed/Fri 11:00; can be cancelled in very wet weather.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the calendar the evening before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rct.uk/visit/the-kings-gallery-buckingham-palace/information-for-groups-visiting-the-kings-gallery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group rate from 15 (£19.80 in 2026); timed arrival; pay 30 days before; Blue Badge guide free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When the 2027 season opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.hrp.org.uk/tower-of-london/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups desk groupsandtraveltrade@hrp.org.uk; group rate from 15; coach driver and Blue Badge guide free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thames boat Tower → London Eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.thamesclippers.com/plan-your-journey/ticket-information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uber Boat: 10% off for groups of 10+; senior discounts. City Cruises if you want live commentary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–4 weeks before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.londoneye.com/tickets-and-prices/groups/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group rate from 10; timed slot 18:15.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dover–Calais ferry with the coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.poferries.com/en/group-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P&amp;O groups line 01304 448899, or DFDS groups uk.groups@dfds.com (dfds.com coach travel). Use the operator's group passport-scan app before Dover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As soon as April 2027 fares open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel Tower – 2nd floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ticket.toureiffel.paris/en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From 29 Sep 2026 groups of more than 9 cannot buy at the ticket office: book online. Tour operators use ticketpro.toureiffel.paris; request the account at least 4 months ahead (tel. +33 892 700 016).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account by Dec 2026; tickets when sales open (~60 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bateauxparisiens.com/en/cruise-tours/guided-tour.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups of 20+ should book ahead; confirm final numbers 3 working days before (tel. +33 1 76 64 14 45).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 months before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louvre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ticket.louvre.fr/en/musee-du-louvre-official-ticketing-service-groups-and-professionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional account required; groups of 7–20 pay a €90 slot fee and €28 per person; a licensed guide must lead each group, so 40 yatris = 2 groups with 2 guides; no cancellation. Group entrance on Rue de Rivoli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the account now; book as soon as April 2027 opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atomium (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.atomium.be/tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group rate 20+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amsterdam canal cruise – Blue Boat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.blueboat.nl/en/canal-cruise-amsterdam/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups: blueboat.nl/en/group-arrangements, info@blueboat.nl, +31 20 679 1370.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keukenhof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://keukenhof.nl/en/groups/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group tickets for 20+ in the online shop (€20.50 online, €26.50 at the gate); date/time changeable up to 24 h before; no cancellation; one barcode per up to 80 people. 2027 season 18 Mar–9 May.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As soon as 2027 group sales open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zaanseschans.com/en/paint-mill-de-kat/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay at the mill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.koelner-dom.de/en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry charge since 1 Jul 2026; free during services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drubba-titisee.com/bootsfahrt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay on board; check that the spring season has started.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhine Falls – Schloss Laufen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://schlosslaufen.ch/en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group 30+ CHF 2 (15–29: CHF 3); group tickets only at the visitor centre; info@schlosslaufen.ch, +41 52 659 67 67.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rhyfall-maendli.ch/linienfahrten-und-erlebnisse/felsenfahrt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not suitable for seniors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount Titlis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.titlis.ch/en/information/prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups of 10+ book in advance at reservation@titlis.ch (online group form); 10% off return tickets (not the Ice Flyer). Book the Trübsee group lunch on the same form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 months before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Lucerne cruise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://webshop.lakelucerne.ch/en/stories/group-bookings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups of 10+: 30% off scheduled boats; book with the group form or groups@lakelucerne.ch (+41 41 367 67 67); tickets collected on the day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luzern–Interlaken Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zentralbahn.ch/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group fare through SBB/zb group desk; seat reservation compulsory (CHF 16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Como boat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.navigazionelaghi.it/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy at Como pier; group and senior rate €4.80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan Duomo (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ticket.duomomilano.it/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groups with their own guide book through the call centre +39 02 89919751 (Mon–Sat 10–17); headsets compulsory for groups of 6+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://palazzoducale.visitmuve.it/en/visitor-information/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group bookings via call centre +39 041 42730892 or prenotazionivenezia@coopculture.it; whisper sets €1 for groups of 10+; licensed guides free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 days before (cheaper online price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice vaporetto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://actv.avmspa.it/en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy day passes at Tronchetto or online (Venezia Unica).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the day or online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice gondola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gondolavenezia.it/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official tariff per gondola (up to 5–6 people); about €90 for 30 min by day. Book through the hotel or a local agent; agree time and price first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 weeks before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venice access fee (day-tripper fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cda.ve.it/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2027 calendar has 72 fee days from 26 March. Guests staying overnight in the Venice municipality (our Mestre hotel) are exempt but must register for the exemption QR code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register 1 week before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-speed trains Venice → Rome → Florence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.trenitalia.com/en.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trenitalia Frecciarossa (or Italo, italotreno.com): book through the group desk for 10+; named tickets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As soon as sales open (~4 months ahead)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tickets.museivaticani.va/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only official site (beware look-alike sites); named tickets; book the 11:00 slot as 2 groups with 2 guides. Ask about the reduced pilgrimage-group ticket (max 20, letter from the religious institution).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As soon as the date opens (~60 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ticketing.colosseo.it/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales open 30 days before; max 25 per group including the guide, so 2 groups; named single tickets (names changeable once, up to 1 week before); helpdesk@ticketcolosseo.com.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactly 30 days before (31 Mar 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevi Fountain basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.comune.roma.it/web/it/notizia/biglietto-dingresso-fontana-di-trevi.page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€2, pay on site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://direzionemuseiroma.cultura.gov.it/en/pantheon/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€7; online booking advised at busy times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 week before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florence Duomo – Brunelleschi Pass (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tickets.duomo.firenze.it/en/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online orders are capped at 10 tickets: email the Opera for a group; named tickets; dome time slot cannot be changed. Cathedral itself free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaning Tower of Pisa (optional climb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.opapisa.it/en/tickets/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each ticket covers up to 30 people, so 2 orders; sales open 15 days before; agencies use the operators' area. Young children cannot climb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 days before (16 Apr 2027)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pros</t>
   </si>
   <si>
@@ -2656,7 +3014,7 @@
     <t xml:space="preserve">Budget shortfall</t>
   </si>
   <si>
-    <t xml:space="preserve">Realistic cost about ₹5.32 lakh per yatri at 40 yatris vs ₹5.00 lakh price.</t>
+    <t xml:space="preserve">Realistic cost about ₹5.33 lakh per yatri at 40 yatris vs ₹5.00 lakh price.</t>
   </si>
   <si>
     <t xml:space="preserve">Group hotel contracts, split UK/mainland coach, fill the coach to 45–49, review price (see Budget).</t>
@@ -3749,111 +4107,167 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>878</v>
+        <v>955</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>956</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>880</v>
+        <v>958</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>959</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>882</v>
+        <v>961</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>962</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>884</v>
+        <v>964</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>885</v>
+        <v>965</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>886</v>
+        <v>967</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>887</v>
+        <v>968</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>969</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>888</v>
+        <v>970</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>971</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>890</v>
+        <v>973</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>974</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>892</v>
+        <v>976</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>893</v>
+        <v>977</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>894</v>
+        <v>979</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>895</v>
+        <v>980</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>896</v>
+        <v>982</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>983</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>898</v>
+        <v>985</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>986</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>900</v>
-      </c>
-      <c r="B13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>988</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>901</v>
-      </c>
-      <c r="B14" s="11"/>
+        <v>991</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>995</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>996</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3871,128 +4285,111 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>902</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>998</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>903</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>999</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>906</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>907</v>
-      </c>
-      <c r="C5" s="11"/>
+        <v>1004</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>908</v>
+        <v>1005</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>909</v>
-      </c>
-      <c r="C6" s="11"/>
+        <v>1006</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>910</v>
+        <v>1007</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>911</v>
-      </c>
-      <c r="C7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>912</v>
+        <v>1009</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>913</v>
-      </c>
-      <c r="C8" s="11"/>
+        <v>1010</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>914</v>
+        <v>1011</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>915</v>
-      </c>
-      <c r="C9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>916</v>
+        <v>1013</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>917</v>
-      </c>
-      <c r="C10" s="11"/>
+        <v>1014</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>918</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>919</v>
-      </c>
-      <c r="C11" s="11"/>
+        <v>1016</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>920</v>
+        <v>1017</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>921</v>
-      </c>
-      <c r="C12" s="11"/>
+        <v>1018</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>922</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>923</v>
-      </c>
-      <c r="C13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1019</v>
+      </c>
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>924</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>925</v>
-      </c>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>926</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>927</v>
-      </c>
-      <c r="C15" s="11"/>
+        <v>1020</v>
+      </c>
+      <c r="B14" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4010,68 +4407,128 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>928</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>929</v>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>930</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>932</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>934</v>
+        <v>1025</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1026</v>
+      </c>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>936</v>
-      </c>
-      <c r="B6" s="11"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1027</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>937</v>
-      </c>
-      <c r="B7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1029</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>938</v>
-      </c>
-      <c r="B8" s="11"/>
+        <v>1031</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>939</v>
-      </c>
-      <c r="B9" s="11"/>
+        <v>1033</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C12" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C15" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4089,6 +4546,85 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B9" s="11"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4098,18 +4634,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>940</v>
+        <v>1059</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>941</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>942</v>
+        <v>1061</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>943</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4117,23 +4653,23 @@
         <v>41</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>944</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>945</v>
+        <v>1064</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>946</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>947</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>948</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4141,31 +4677,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>949</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>950</v>
+        <v>1069</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>951</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>952</v>
+        <v>1071</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>953</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>954</v>
+        <v>1073</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>955</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,23 +4709,23 @@
         <v>287</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>956</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>957</v>
+        <v>1076</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>958</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>959</v>
+        <v>1078</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>960</v>
+        <v>1079</v>
       </c>
     </row>
   </sheetData>
@@ -4943,18 +5479,18 @@
       </c>
       <c r="E39" s="13" t="n">
         <f aca="false">'Entry tickets'!F47</f>
-        <v>53351.524</v>
+        <v>54177.076</v>
       </c>
       <c r="F39" s="13" t="n">
         <v>50000</v>
       </c>
       <c r="G39" s="13" t="n">
         <f aca="false">IF(F39="","",E39-F39)</f>
-        <v>3351.524</v>
+        <v>4177.076</v>
       </c>
       <c r="H39" s="13" t="n">
         <f aca="false">E39*$B$4</f>
-        <v>2134060.96</v>
+        <v>2167083.04</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>97</v>
@@ -5177,7 +5713,7 @@
       <c r="D47" s="11"/>
       <c r="E47" s="17" t="n">
         <f aca="false">SUM(E27:E46)</f>
-        <v>506476.579</v>
+        <v>507302.131</v>
       </c>
       <c r="F47" s="17" t="n">
         <f aca="false">SUM(F27:F46)</f>
@@ -5186,7 +5722,7 @@
       <c r="G47" s="11"/>
       <c r="H47" s="17" t="n">
         <f aca="false">E47*$B$4</f>
-        <v>20259063.16</v>
+        <v>20292085.24</v>
       </c>
       <c r="I47" s="11"/>
     </row>
@@ -5199,13 +5735,13 @@
       <c r="D48" s="11"/>
       <c r="E48" s="17" t="n">
         <f aca="false">E47*$B$6</f>
-        <v>25323.82895</v>
+        <v>25365.10655</v>
       </c>
       <c r="F48" s="17"/>
       <c r="G48" s="11"/>
       <c r="H48" s="17" t="n">
         <f aca="false">E48*$B$4</f>
-        <v>1012953.158</v>
+        <v>1014604.262</v>
       </c>
       <c r="I48" s="11"/>
     </row>
@@ -5218,7 +5754,7 @@
       <c r="D49" s="11"/>
       <c r="E49" s="17" t="n">
         <f aca="false">E47+E48</f>
-        <v>531800.40795</v>
+        <v>532667.23755</v>
       </c>
       <c r="F49" s="17" t="n">
         <f aca="false">F47</f>
@@ -5227,7 +5763,7 @@
       <c r="G49" s="11"/>
       <c r="H49" s="17" t="n">
         <f aca="false">E49*$B$4</f>
-        <v>21272016.318</v>
+        <v>21306689.502</v>
       </c>
       <c r="I49" s="11"/>
     </row>
@@ -5259,7 +5795,7 @@
       <c r="D51" s="11"/>
       <c r="E51" s="17" t="n">
         <f aca="false">E50-E49</f>
-        <v>-31800.40795</v>
+        <v>-32667.23755</v>
       </c>
       <c r="F51" s="17" t="n">
         <f aca="false">F50-F49</f>
@@ -5268,7 +5804,7 @@
       <c r="G51" s="11"/>
       <c r="H51" s="17" t="n">
         <f aca="false">E51*$B$4</f>
-        <v>-1272016.318</v>
+        <v>-1306689.502</v>
       </c>
       <c r="I51" s="11"/>
     </row>
@@ -5281,7 +5817,7 @@
       <c r="D52" s="11"/>
       <c r="E52" s="18" t="n">
         <f aca="false">E51/E50</f>
-        <v>-0.0636008159000001</v>
+        <v>-0.0653344750999999</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">F51/F50</f>
@@ -5300,7 +5836,7 @@
       <c r="D53" s="11"/>
       <c r="E53" s="17" t="n">
         <f aca="false">E49/0.95</f>
-        <v>559789.903105263</v>
+        <v>560702.35531579</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="11"/>
@@ -5336,16 +5872,16 @@
       <c r="D56" s="11"/>
       <c r="E56" s="19" t="n">
         <f aca="false">(SUMIFS(E27:E46,B27:B46,"&lt;&gt;group")+SUMIFS(H27:H46,B27:B46,"group")/B56)*(1+$B$6)</f>
-        <v>568240.88545</v>
+        <v>569107.71505</v>
       </c>
       <c r="F56" s="19" t="n">
         <f aca="false">$B$5-E56</f>
-        <v>-68240.8854500001</v>
+        <v>-69107.71505</v>
       </c>
       <c r="G56" s="11"/>
       <c r="H56" s="19" t="n">
         <f aca="false">F56*B56</f>
-        <v>-2047226.5635</v>
+        <v>-2073231.4515</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5357,16 +5893,16 @@
       <c r="D57" s="11"/>
       <c r="E57" s="19" t="n">
         <f aca="false">(SUMIFS(E27:E46,B27:B46,"&lt;&gt;group")+SUMIFS(H27:H46,B27:B46,"group")/B57)*(1+$B$6)</f>
-        <v>547417.75545</v>
+        <v>548284.58505</v>
       </c>
       <c r="F57" s="19" t="n">
         <f aca="false">$B$5-E57</f>
-        <v>-47417.7554500001</v>
+        <v>-48284.58505</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="19" t="n">
         <f aca="false">F57*B57</f>
-        <v>-1659621.44075</v>
+        <v>-1689960.47675</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5378,16 +5914,16 @@
       <c r="D58" s="11"/>
       <c r="E58" s="19" t="n">
         <f aca="false">(SUMIFS(E27:E46,B27:B46,"&lt;&gt;group")+SUMIFS(H27:H46,B27:B46,"group")/B58)*(1+$B$6)</f>
-        <v>531800.40795</v>
+        <v>532667.23755</v>
       </c>
       <c r="F58" s="19" t="n">
         <f aca="false">$B$5-E58</f>
-        <v>-31800.40795</v>
+        <v>-32667.23755</v>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="19" t="n">
         <f aca="false">F58*B58</f>
-        <v>-1272016.318</v>
+        <v>-1306689.502</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5399,16 +5935,16 @@
       <c r="D59" s="11"/>
       <c r="E59" s="19" t="n">
         <f aca="false">(SUMIFS(E27:E46,B27:B46,"&lt;&gt;group")+SUMIFS(H27:H46,B27:B46,"group")/B59)*(1+$B$6)</f>
-        <v>519653.582116667</v>
+        <v>520520.411716667</v>
       </c>
       <c r="F59" s="19" t="n">
         <f aca="false">$B$5-E59</f>
-        <v>-19653.5821166667</v>
+        <v>-20520.4117166667</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="19" t="n">
         <f aca="false">F59*B59</f>
-        <v>-884411.19525</v>
+        <v>-923418.52725</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,16 +5956,16 @@
       <c r="D60" s="11"/>
       <c r="E60" s="19" t="n">
         <f aca="false">(SUMIFS(E27:E46,B27:B46,"&lt;&gt;group")+SUMIFS(H27:H46,B27:B46,"group")/B60)*(1+$B$6)</f>
-        <v>511720.961164286</v>
+        <v>512587.790764286</v>
       </c>
       <c r="F60" s="19" t="n">
         <f aca="false">$B$5-E60</f>
-        <v>-11720.9611642857</v>
+        <v>-12587.7907642857</v>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="19" t="n">
         <f aca="false">F60*B60</f>
-        <v>-574327.09705</v>
+        <v>-616801.747449997</v>
       </c>
     </row>
   </sheetData>
@@ -21313,7 +21849,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="n">
         <v>8</v>
       </c>
@@ -21394,7 +21930,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="n">
         <v>10</v>
       </c>
@@ -21408,11 +21944,11 @@
         <v>52</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">IF(E30="","",E30*$B$6)</f>
-        <v>573.3</v>
+        <v>229.32</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>766</v>
@@ -21448,7 +21984,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="n">
         <v>11</v>
       </c>
@@ -21462,11 +21998,11 @@
         <v>52</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>81.6</v>
+        <v>91.8</v>
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">IF(E32="","",E32*$B$6)</f>
-        <v>9356.256</v>
+        <v>10525.788</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>770</v>
@@ -21502,7 +22038,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="n">
         <v>11</v>
       </c>
@@ -21658,7 +22194,9 @@
       <c r="G39" s="11" t="s">
         <v>784</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="30" t="s">
+        <v>728</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="n">
@@ -21859,7 +22397,7 @@
       <c r="E47" s="11"/>
       <c r="F47" s="25" t="n">
         <f aca="false">SUMIFS(F10:F46,C10:C46,"Yes")</f>
-        <v>53351.524</v>
+        <v>54177.076</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
@@ -21915,13 +22453,14 @@
     <hyperlink ref="H36" r:id="rId27" display="Open"/>
     <hyperlink ref="H37" r:id="rId28" display="Open"/>
     <hyperlink ref="H38" r:id="rId29" display="Open"/>
-    <hyperlink ref="H40" r:id="rId30" display="Open"/>
-    <hyperlink ref="H41" r:id="rId31" display="Open"/>
-    <hyperlink ref="H42" r:id="rId32" display="Open"/>
-    <hyperlink ref="H43" r:id="rId33" display="Open"/>
-    <hyperlink ref="H44" r:id="rId34" display="Open"/>
-    <hyperlink ref="H45" r:id="rId35" display="Open"/>
-    <hyperlink ref="H46" r:id="rId36" display="Open"/>
+    <hyperlink ref="H39" r:id="rId30" display="Open"/>
+    <hyperlink ref="H40" r:id="rId31" display="Open"/>
+    <hyperlink ref="H41" r:id="rId32" display="Open"/>
+    <hyperlink ref="H42" r:id="rId33" display="Open"/>
+    <hyperlink ref="H43" r:id="rId34" display="Open"/>
+    <hyperlink ref="H44" r:id="rId35" display="Open"/>
+    <hyperlink ref="H45" r:id="rId36" display="Open"/>
+    <hyperlink ref="H46" r:id="rId37" display="Open"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21938,198 +22477,648 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>802</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="B3" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="20" t="s">
         <v>804</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="20" t="s">
         <v>805</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>806</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>809</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>808</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>810</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>812</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
-        <v>6</v>
-      </c>
       <c r="B8" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>816</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>814</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>816</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>821</v>
+        <v>825</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>826</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>822</v>
+        <v>277</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>828</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>831</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>827</v>
+        <v>835</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>828</v>
+        <v>747</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>838</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>831</v>
+        <v>842</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>843</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>832</v>
+        <v>845</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>833</v>
+        <v>846</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>835</v>
+        <v>849</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>859</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>860</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>866</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>869</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>891</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>908</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>909</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>910</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>912</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>915</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>919</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -22148,166 +23137,198 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>836</v>
+        <v>122</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>837</v>
+        <v>921</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>839</v>
+        <v>922</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>840</v>
+        <v>923</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>841</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>842</v>
+      <c r="A4" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>843</v>
+        <v>925</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>844</v>
+        <v>926</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>845</v>
+      <c r="A5" s="11" t="n">
+        <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>846</v>
+        <v>927</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>847</v>
+        <v>928</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>848</v>
+      <c r="A6" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>849</v>
+        <v>929</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>850</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>851</v>
+      <c r="A7" s="11" t="n">
+        <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>852</v>
+        <v>931</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>854</v>
+        <v>932</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>855</v>
+        <v>933</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>857</v>
+        <v>934</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
+        <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>858</v>
+        <v>935</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>860</v>
+        <v>936</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>861</v>
+        <v>937</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>862</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>863</v>
+      <c r="A11" s="11" t="n">
+        <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>864</v>
+        <v>939</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>866</v>
+        <v>940</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>867</v>
+        <v>941</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>869</v>
+        <v>942</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>870</v>
+        <v>943</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>872</v>
+        <v>944</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>873</v>
+        <v>945</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>875</v>
+        <v>946</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>876</v>
+        <v>947</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>877</v>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>954</v>
       </c>
     </row>
   </sheetData>

--- a/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
+++ b/itineraries/london-europe-yatra/London_Europe_Yatra_Minute_Itinerary.xlsx
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Package price</t>
   </si>
   <si>
-    <t xml:space="preserve">₹5,00,000 per person (all inclusive, all flights) + 5% GST + 5% TCS (TCS claimable against income tax)</t>
+    <t xml:space="preserve">₹5,49,000 per person (including international flights) + 5% GST + 2% TCS (TCS refunded/credited through your income-tax return)</t>
   </si>
   <si>
     <t xml:space="preserve">Mode of transport</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">2024 posters (15N/16D, 8 countries), brochure PDF, inclusions/exclusions sheet, Schengen biometric guidelines, shortlisted 2027 flights, team budget sheet; prices and events checked 22 Oct 2026.</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget per yatri – cost against the ₹5,00,000 price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue cells are inputs. Group costs are divided by the number of yatris. GST (5%) and TCS (5%) are collected on top of the price and passed on, so they are not costs here.</t>
+    <t xml:space="preserve">Budget per yatri – cost against the ₹5,49,000 price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue cells are inputs. Group costs are divided by the number of yatris. GST (5%) and TCS (2%) are collected on top of the price and passed on, so they are not costs here.</t>
   </si>
   <si>
     <t xml:space="preserve">Yatris (paying)</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">UK first (mid-to-late Jan 2027), then Schengen via Italy (by late Feb / early Mar 2027).</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget shortfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realistic cost about ₹5.33 lakh per yatri at 40 yatris vs ₹5.00 lakh price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group hotel contracts, split UK/mainland coach, fill the coach to 45–49, review price (see Budget).</t>
+    <t xml:space="preserve">Thin margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realistic cost about ₹5.33 lakh per yatri at 40 yatris vs the ₹5.49 lakh price: a margin of only about 3%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock hotel, coach and flight prices early; hold the contingency; fill the coach to 45–49 (see Budget).</t>
   </si>
   <si>
     <t xml:space="preserve">Lost passport or luggage</t>
@@ -4779,7 +4779,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>500000</v>
+        <v>549000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5776,11 +5776,11 @@
       <c r="D50" s="11"/>
       <c r="E50" s="17" t="n">
         <f aca="false">$B$5</f>
-        <v>500000</v>
+        <v>549000</v>
       </c>
       <c r="F50" s="17" t="n">
         <f aca="false">$B$5</f>
-        <v>500000</v>
+        <v>549000</v>
       </c>
       <c r="G50" s="11"/>
       <c r="H50" s="17"/>
@@ -5795,16 +5795,16 @@
       <c r="D51" s="11"/>
       <c r="E51" s="17" t="n">
         <f aca="false">E50-E49</f>
-        <v>-32667.23755</v>
+        <v>16332.76245</v>
       </c>
       <c r="F51" s="17" t="n">
         <f aca="false">F50-F49</f>
-        <v>83000</v>
+        <v>132000</v>
       </c>
       <c r="G51" s="11"/>
       <c r="H51" s="17" t="n">
         <f aca="false">E51*$B$4</f>
-        <v>-1306689.502</v>
+        <v>653310.498000002</v>
       </c>
       <c r="I51" s="11"/>
     </row>
@@ -5817,11 +5817,11 @@
       <c r="D52" s="11"/>
       <c r="E52" s="18" t="n">
         <f aca="false">E51/E50</f>
-        <v>-0.0653344750999999</v>
+        <v>0.0297500226775957</v>
       </c>
       <c r="F52" s="18" t="n">
         <f aca="false">F51/F50</f>
-        <v>0.166</v>
+        <v>0.240437158469945</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="18"/>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="F56" s="19" t="n">
         <f aca="false">$B$5-E56</f>
-        <v>-69107.71505</v>
+        <v>-20107.71505</v>
       </c>
       <c r="G56" s="11"/>
       <c r="H56" s="19" t="n">
         <f aca="false">F56*B56</f>
-        <v>-2073231.4515</v>
+        <v>-603231.4515</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="F57" s="19" t="n">
         <f aca="false">$B$5-E57</f>
-        <v>-48284.58505</v>
+        <v>715.414950000006</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="19" t="n">
         <f aca="false">F57*B57</f>
-        <v>-1689960.47675</v>
+        <v>25039.5232500002</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="F58" s="19" t="n">
         <f aca="false">$B$5-E58</f>
-        <v>-32667.23755</v>
+        <v>16332.76245</v>
       </c>
       <c r="G58" s="11"/>
       <c r="H58" s="19" t="n">
         <f aca="false">F58*B58</f>
-        <v>-1306689.502</v>
+        <v>653310.498000002</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="F59" s="19" t="n">
         <f aca="false">$B$5-E59</f>
-        <v>-20520.4117166667</v>
+        <v>28479.5882833333</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="19" t="n">
         <f aca="false">F59*B59</f>
-        <v>-923418.52725</v>
+        <v>1281581.47275</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="F60" s="19" t="n">
         <f aca="false">$B$5-E60</f>
-        <v>-12587.7907642857</v>
+        <v>36412.2092357143</v>
       </c>
       <c r="G60" s="11"/>
       <c r="H60" s="19" t="n">
         <f aca="false">F60*B60</f>
-        <v>-616801.747449997</v>
+        <v>1784198.25255</v>
       </c>
     </row>
   </sheetData>
